--- a/Data/EXCEL/Transfer/salemon/20240711/8083-salemon-20240711.xlsx
+++ b/Data/EXCEL/Transfer/salemon/20240711/8083-salemon-20240711.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlsx\20240711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\salemon\20240711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9A66612-7877-447A-ABE2-D82FD0EF80F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{43DFEC39-DC73-4C1D-94B9-28F351CCA9AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="290" windowWidth="18240" windowHeight="13390" xr2:uid="{F1293B6A-050E-474A-ABDB-BB576F5DCB21}"/>
+    <workbookView xWindow="768" yWindow="684" windowWidth="20004" windowHeight="13956" xr2:uid="{3EBBB47B-B4BE-4650-8A36-FAA15B624366}"/>
   </bookViews>
   <sheets>
     <sheet name="8083-salemon-20240711" sheetId="2" r:id="rId1"/>
@@ -1261,25 +1261,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{822894CD-3CE9-47E1-9D79-5F72BE15E5A4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F2A5B41-FE8F-445F-8A1E-C130B026E9F4}">
   <dimension ref="A1:Q498"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1306,7 +1306,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="15" t="s">
         <v>4</v>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1388,7 +1388,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1427,7 +1427,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>45444</v>
       </c>
@@ -1480,7 +1480,7 @@
         <v>75.7</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>45413</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>87.8</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>45383</v>
       </c>
@@ -1586,7 +1586,7 @@
         <v>91.8</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>45352</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>78.900000000000006</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>45323</v>
       </c>
@@ -1692,7 +1692,7 @@
         <v>80.400000000000006</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>45292</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>98.1</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>45261</v>
       </c>
@@ -1798,7 +1798,7 @@
         <v>-34.299999999999997</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>45231</v>
       </c>
@@ -1851,7 +1851,7 @@
         <v>-36.799999999999997</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>45200</v>
       </c>
@@ -1904,7 +1904,7 @@
         <v>-39.200000000000003</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <v>45170</v>
       </c>
@@ -1957,7 +1957,7 @@
         <v>-41.9</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>45139</v>
       </c>
@@ -2010,7 +2010,7 @@
         <v>-46</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>45108</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>-48.9</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>45078</v>
       </c>
@@ -2116,7 +2116,7 @@
         <v>-51.3</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>45047</v>
       </c>
@@ -2169,7 +2169,7 @@
         <v>-52.9</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>45017</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>-55.3</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>44986</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>-56.2</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>44958</v>
       </c>
@@ -2328,7 +2328,7 @@
         <v>-59.7</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>44927</v>
       </c>
@@ -2381,7 +2381,7 @@
         <v>-67.599999999999994</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>44896</v>
       </c>
@@ -2434,7 +2434,7 @@
         <v>-26.8</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>44866</v>
       </c>
@@ -2487,7 +2487,7 @@
         <v>-25.6</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>44835</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v>-22.5</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>44805</v>
       </c>
@@ -2593,7 +2593,7 @@
         <v>-20.6</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>44774</v>
       </c>
@@ -2646,7 +2646,7 @@
         <v>-17.899999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>44743</v>
       </c>
@@ -2699,7 +2699,7 @@
         <v>-17.5</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>44713</v>
       </c>
@@ -2752,7 +2752,7 @@
         <v>-17.600000000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>44682</v>
       </c>
@@ -2805,7 +2805,7 @@
         <v>-17</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>44652</v>
       </c>
@@ -2858,7 +2858,7 @@
         <v>-13.9</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>44621</v>
       </c>
@@ -2911,7 +2911,7 @@
         <v>-7.62</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>44593</v>
       </c>
@@ -2964,7 +2964,7 @@
         <v>-7.73</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>44562</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>44531</v>
       </c>
@@ -3070,7 +3070,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>44501</v>
       </c>
@@ -3123,7 +3123,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>44470</v>
       </c>
@@ -3176,7 +3176,7 @@
         <v>30.8</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>44440</v>
       </c>
@@ -3229,7 +3229,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>44409</v>
       </c>
@@ -3282,7 +3282,7 @@
         <v>45.9</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>44378</v>
       </c>
@@ -3335,7 +3335,7 @@
         <v>48.2</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>44348</v>
       </c>
@@ -3388,7 +3388,7 @@
         <v>48.3</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>44317</v>
       </c>
@@ -3441,7 +3441,7 @@
         <v>43.9</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>44287</v>
       </c>
@@ -3494,7 +3494,7 @@
         <v>42.7</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>44256</v>
       </c>
@@ -3547,7 +3547,7 @@
         <v>40.200000000000003</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>44228</v>
       </c>
@@ -3600,7 +3600,7 @@
         <v>40.9</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>44197</v>
       </c>
@@ -3653,7 +3653,7 @@
         <v>44.2</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>44166</v>
       </c>
@@ -3706,7 +3706,7 @@
         <v>27.9</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>44136</v>
       </c>
@@ -3759,7 +3759,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>44105</v>
       </c>
@@ -3812,7 +3812,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
         <v>44075</v>
       </c>
@@ -3865,7 +3865,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>44044</v>
       </c>
@@ -3918,7 +3918,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="10">
         <v>44013</v>
       </c>
@@ -3971,7 +3971,7 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>43983</v>
       </c>
@@ -4024,7 +4024,7 @@
         <v>3.89</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="10">
         <v>43952</v>
       </c>
@@ -4077,7 +4077,7 @@
         <v>2.77</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>43922</v>
       </c>
@@ -4130,7 +4130,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="10">
         <v>43891</v>
       </c>
@@ -4183,7 +4183,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>43862</v>
       </c>
@@ -4236,7 +4236,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="10">
         <v>43831</v>
       </c>
@@ -4289,7 +4289,7 @@
         <v>-10.199999999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>43800</v>
       </c>
@@ -4342,7 +4342,7 @@
         <v>6.63</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="10">
         <v>43770</v>
       </c>
@@ -4395,7 +4395,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>43739</v>
       </c>
@@ -4448,7 +4448,7 @@
         <v>7.13</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="10">
         <v>43709</v>
       </c>
@@ -4501,7 +4501,7 @@
         <v>7.83</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>43678</v>
       </c>
@@ -4554,7 +4554,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="10">
         <v>43647</v>
       </c>
@@ -4607,7 +4607,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>43617</v>
       </c>
@@ -4660,7 +4660,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="10">
         <v>43586</v>
       </c>
@@ -4713,7 +4713,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>43556</v>
       </c>
@@ -4766,7 +4766,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="10">
         <v>43525</v>
       </c>
@@ -4819,7 +4819,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>43497</v>
       </c>
@@ -4872,7 +4872,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="10">
         <v>43466</v>
       </c>
@@ -4925,7 +4925,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>43435</v>
       </c>
@@ -4978,7 +4978,7 @@
         <v>2.41</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="10">
         <v>43405</v>
       </c>
@@ -5031,7 +5031,7 @@
         <v>1.63</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>43374</v>
       </c>
@@ -5084,7 +5084,7 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="10">
         <v>43344</v>
       </c>
@@ -5137,7 +5137,7 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>43313</v>
       </c>
@@ -5190,7 +5190,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="10">
         <v>43282</v>
       </c>
@@ -5243,7 +5243,7 @@
         <v>-0.51</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>43252</v>
       </c>
@@ -5296,7 +5296,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="10">
         <v>43221</v>
       </c>
@@ -5349,7 +5349,7 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>43191</v>
       </c>
@@ -5402,7 +5402,7 @@
         <v>2.0099999999999998</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="10">
         <v>43160</v>
       </c>
@@ -5455,7 +5455,7 @@
         <v>3.41</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>43132</v>
       </c>
@@ -5508,7 +5508,7 @@
         <v>4.47</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="10">
         <v>43101</v>
       </c>
@@ -5561,7 +5561,7 @@
         <v>5.71</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>43070</v>
       </c>
@@ -5614,7 +5614,7 @@
         <v>-3.03</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="10">
         <v>43040</v>
       </c>
@@ -5667,7 +5667,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="5">
         <v>43009</v>
       </c>
@@ -5720,7 +5720,7 @@
         <v>-3.39</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="10">
         <v>42979</v>
       </c>
@@ -5773,7 +5773,7 @@
         <v>-3.69</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="5">
         <v>42948</v>
       </c>
@@ -5826,7 +5826,7 @@
         <v>-3.11</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="10">
         <v>42917</v>
       </c>
@@ -5879,7 +5879,7 @@
         <v>-2.09</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="5">
         <v>42887</v>
       </c>
@@ -5932,7 +5932,7 @@
         <v>-0.76</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="10">
         <v>42856</v>
       </c>
@@ -5985,7 +5985,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="5">
         <v>42826</v>
       </c>
@@ -6038,7 +6038,7 @@
         <v>3.07</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" s="10">
         <v>42795</v>
       </c>
@@ -6091,7 +6091,7 @@
         <v>5.96</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="5">
         <v>42767</v>
       </c>
@@ -6144,7 +6144,7 @@
         <v>1.94</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="10">
         <v>42736</v>
       </c>
@@ -6197,7 +6197,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="5">
         <v>42705</v>
       </c>
@@ -6250,7 +6250,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="10">
         <v>42675</v>
       </c>
@@ -6303,7 +6303,7 @@
         <v>9.8800000000000008</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" s="5">
         <v>42644</v>
       </c>
@@ -6356,7 +6356,7 @@
         <v>8.2799999999999994</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" s="10">
         <v>42614</v>
       </c>
@@ -6409,7 +6409,7 @@
         <v>7.88</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" s="5">
         <v>42583</v>
       </c>
@@ -6462,7 +6462,7 @@
         <v>7.41</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" s="10">
         <v>42552</v>
       </c>
@@ -6515,7 +6515,7 @@
         <v>6.12</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" s="5">
         <v>42522</v>
       </c>
@@ -6568,7 +6568,7 @@
         <v>5.07</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" s="10">
         <v>42491</v>
       </c>
@@ -6621,7 +6621,7 @@
         <v>2.39</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" s="5">
         <v>42461</v>
       </c>
@@ -6674,7 +6674,7 @@
         <v>-2.3199999999999998</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" s="10">
         <v>42430</v>
       </c>
@@ -6727,7 +6727,7 @@
         <v>-3.78</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" s="5">
         <v>42401</v>
       </c>
@@ -6780,7 +6780,7 @@
         <v>-3.78</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" s="10">
         <v>42370</v>
       </c>
@@ -6833,7 +6833,7 @@
         <v>-6.67</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" s="5">
         <v>42339</v>
       </c>
@@ -6886,7 +6886,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" s="10">
         <v>42309</v>
       </c>
@@ -6939,7 +6939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" s="5">
         <v>42278</v>
       </c>
@@ -6992,7 +6992,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" s="10">
         <v>42248</v>
       </c>
@@ -7045,7 +7045,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" s="5">
         <v>42217</v>
       </c>
@@ -7098,7 +7098,7 @@
         <v>3.37</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" s="10">
         <v>42186</v>
       </c>
@@ -7151,7 +7151,7 @@
         <v>4.76</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" s="5">
         <v>42156</v>
       </c>
@@ -7204,7 +7204,7 @@
         <v>6.69</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" s="10">
         <v>42125</v>
       </c>
@@ -7257,7 +7257,7 @@
         <v>7.94</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" s="5">
         <v>42095</v>
       </c>
@@ -7310,7 +7310,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" s="10">
         <v>42064</v>
       </c>
@@ -7363,7 +7363,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" s="5">
         <v>42036</v>
       </c>
@@ -7416,7 +7416,7 @@
         <v>9.57</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" s="10">
         <v>42005</v>
       </c>
@@ -7469,7 +7469,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" s="5">
         <v>41974</v>
       </c>
@@ -7522,7 +7522,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" s="10">
         <v>41944</v>
       </c>
@@ -7575,7 +7575,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" s="5">
         <v>41913</v>
       </c>
@@ -7628,7 +7628,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" s="10">
         <v>41883</v>
       </c>
@@ -7681,7 +7681,7 @@
         <v>28.2</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" s="5">
         <v>41852</v>
       </c>
@@ -7734,7 +7734,7 @@
         <v>27.3</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" s="10">
         <v>41821</v>
       </c>
@@ -7787,7 +7787,7 @@
         <v>28.1</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" s="5">
         <v>41791</v>
       </c>
@@ -7840,7 +7840,7 @@
         <v>27.3</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" s="10">
         <v>41760</v>
       </c>
@@ -7893,7 +7893,7 @@
         <v>30.8</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" s="5">
         <v>41730</v>
       </c>
@@ -7946,7 +7946,7 @@
         <v>33.4</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" s="10">
         <v>41699</v>
       </c>
@@ -7999,7 +7999,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" s="5">
         <v>41671</v>
       </c>
@@ -8052,7 +8052,7 @@
         <v>34.6</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" s="10">
         <v>41640</v>
       </c>
@@ -8105,7 +8105,7 @@
         <v>36.4</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" s="5">
         <v>41609</v>
       </c>
@@ -8158,7 +8158,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" s="10">
         <v>41579</v>
       </c>
@@ -8211,7 +8211,7 @@
         <v>9.07</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" s="5">
         <v>41548</v>
       </c>
@@ -8264,7 +8264,7 @@
         <v>7.39</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A134" s="10">
         <v>41518</v>
       </c>
@@ -8317,7 +8317,7 @@
         <v>5.83</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A135" s="5">
         <v>41487</v>
       </c>
@@ -8370,7 +8370,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A136" s="10">
         <v>41456</v>
       </c>
@@ -8423,7 +8423,7 @@
         <v>3.73</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" s="5">
         <v>41426</v>
       </c>
@@ -8476,7 +8476,7 @@
         <v>3.24</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" s="10">
         <v>41395</v>
       </c>
@@ -8529,7 +8529,7 @@
         <v>-1.19</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" s="5">
         <v>41365</v>
       </c>
@@ -8582,7 +8582,7 @@
         <v>-2.79</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A140" s="10">
         <v>41334</v>
       </c>
@@ -8635,7 +8635,7 @@
         <v>-2.98</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A141" s="5">
         <v>41306</v>
       </c>
@@ -8688,7 +8688,7 @@
         <v>-5.25</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A142" s="10">
         <v>41275</v>
       </c>
@@ -8741,7 +8741,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A143" s="5">
         <v>41244</v>
       </c>
@@ -8794,7 +8794,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A144" s="10">
         <v>41214</v>
       </c>
@@ -8847,7 +8847,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A145" s="5">
         <v>41183</v>
       </c>
@@ -8900,7 +8900,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A146" s="10">
         <v>41153</v>
       </c>
@@ -8953,7 +8953,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A147" s="5">
         <v>41122</v>
       </c>
@@ -9006,7 +9006,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A148" s="10">
         <v>41091</v>
       </c>
@@ -9059,7 +9059,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A149" s="5">
         <v>41061</v>
       </c>
@@ -9112,7 +9112,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A150" s="10">
         <v>41030</v>
       </c>
@@ -9165,7 +9165,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A151" s="5">
         <v>41000</v>
       </c>
@@ -9218,7 +9218,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A152" s="10">
         <v>40969</v>
       </c>
@@ -9271,7 +9271,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A153" s="5">
         <v>40940</v>
       </c>
@@ -9324,7 +9324,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A154" s="10">
         <v>40909</v>
       </c>
@@ -9377,7 +9377,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A155" s="5">
         <v>40878</v>
       </c>
@@ -9430,7 +9430,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A156" s="10">
         <v>40848</v>
       </c>
@@ -9483,7 +9483,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A157" s="5">
         <v>40817</v>
       </c>
@@ -9536,7 +9536,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A158" s="10">
         <v>40787</v>
       </c>
@@ -9589,7 +9589,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A159" s="5">
         <v>40756</v>
       </c>
@@ -9642,7 +9642,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A160" s="10">
         <v>40725</v>
       </c>
@@ -9695,7 +9695,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A161" s="5">
         <v>40695</v>
       </c>
@@ -9748,7 +9748,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A162" s="10">
         <v>40664</v>
       </c>
@@ -9801,7 +9801,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A163" s="5">
         <v>40634</v>
       </c>
@@ -9854,7 +9854,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A164" s="10">
         <v>40603</v>
       </c>
@@ -9907,7 +9907,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A165" s="5">
         <v>40575</v>
       </c>
@@ -9960,7 +9960,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A166" s="10">
         <v>40544</v>
       </c>
@@ -10013,7 +10013,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A167" s="5">
         <v>40513</v>
       </c>
@@ -10066,7 +10066,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A168" s="10">
         <v>40483</v>
       </c>
@@ -10119,7 +10119,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A169" s="5">
         <v>40452</v>
       </c>
@@ -10172,7 +10172,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A170" s="10">
         <v>40422</v>
       </c>
@@ -10225,7 +10225,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A171" s="5">
         <v>40391</v>
       </c>
@@ -10278,7 +10278,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A172" s="10">
         <v>40360</v>
       </c>
@@ -10331,7 +10331,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A173" s="5">
         <v>40330</v>
       </c>
@@ -10384,7 +10384,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A174" s="10">
         <v>40299</v>
       </c>
@@ -10437,7 +10437,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A175" s="5">
         <v>40269</v>
       </c>
@@ -10490,7 +10490,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A176" s="10">
         <v>40238</v>
       </c>
@@ -10543,7 +10543,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A177" s="5">
         <v>40210</v>
       </c>
@@ -10596,7 +10596,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A178" s="10">
         <v>40179</v>
       </c>
@@ -10649,7 +10649,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A179" s="5">
         <v>40148</v>
       </c>
@@ -10702,7 +10702,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A180" s="10">
         <v>40118</v>
       </c>
@@ -10755,7 +10755,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A181" s="5">
         <v>40087</v>
       </c>
@@ -10808,7 +10808,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A182" s="10">
         <v>40057</v>
       </c>
@@ -10861,7 +10861,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A183" s="5">
         <v>40026</v>
       </c>
@@ -10914,7 +10914,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A184" s="10">
         <v>39995</v>
       </c>
@@ -10967,7 +10967,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A185" s="5">
         <v>39965</v>
       </c>
@@ -11020,7 +11020,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A186" s="10">
         <v>39934</v>
       </c>
@@ -11073,7 +11073,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A187" s="5">
         <v>39904</v>
       </c>
@@ -11126,7 +11126,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A188" s="10">
         <v>39873</v>
       </c>
@@ -11179,7 +11179,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A189" s="5">
         <v>39845</v>
       </c>
@@ -11232,7 +11232,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A190" s="10">
         <v>39814</v>
       </c>
@@ -11285,7 +11285,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A191" s="5">
         <v>39783</v>
       </c>
@@ -11338,7 +11338,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A192" s="10">
         <v>39753</v>
       </c>
@@ -11391,7 +11391,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A193" s="5">
         <v>39722</v>
       </c>
@@ -11444,7 +11444,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A194" s="10">
         <v>39692</v>
       </c>
@@ -11497,7 +11497,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A195" s="5">
         <v>39661</v>
       </c>
@@ -11550,7 +11550,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A196" s="10">
         <v>39630</v>
       </c>
@@ -11603,7 +11603,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A197" s="5">
         <v>39600</v>
       </c>
@@ -11656,7 +11656,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A198" s="10">
         <v>39569</v>
       </c>
@@ -11709,7 +11709,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A199" s="5">
         <v>39539</v>
       </c>
@@ -11762,7 +11762,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A200" s="10">
         <v>39508</v>
       </c>
@@ -11815,7 +11815,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A201" s="5">
         <v>39479</v>
       </c>
@@ -11868,7 +11868,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A202" s="10">
         <v>39448</v>
       </c>
@@ -11921,7 +11921,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A203" s="5">
         <v>39417</v>
       </c>
@@ -11974,7 +11974,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A204" s="10">
         <v>39387</v>
       </c>
@@ -12027,7 +12027,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A205" s="5">
         <v>39356</v>
       </c>
@@ -12080,7 +12080,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A206" s="10">
         <v>39326</v>
       </c>
@@ -12133,7 +12133,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A207" s="5">
         <v>39295</v>
       </c>
@@ -12186,7 +12186,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A208" s="10">
         <v>39264</v>
       </c>
@@ -12239,7 +12239,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A209" s="5">
         <v>39234</v>
       </c>
@@ -12292,7 +12292,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A210" s="10">
         <v>39203</v>
       </c>
@@ -12345,7 +12345,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A211" s="5">
         <v>39173</v>
       </c>
@@ -12398,7 +12398,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A212" s="10">
         <v>39142</v>
       </c>
@@ -12451,7 +12451,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A213" s="5">
         <v>39114</v>
       </c>
@@ -12504,7 +12504,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A214" s="10">
         <v>39083</v>
       </c>
@@ -12557,7 +12557,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A215" s="5">
         <v>39052</v>
       </c>
@@ -12610,7 +12610,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A216" s="10">
         <v>39022</v>
       </c>
@@ -12663,7 +12663,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A217" s="5">
         <v>38991</v>
       </c>
@@ -12716,7 +12716,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A218" s="10">
         <v>38961</v>
       </c>
@@ -12769,7 +12769,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A219" s="5">
         <v>38930</v>
       </c>
@@ -12822,7 +12822,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A220" s="10">
         <v>38899</v>
       </c>
@@ -12875,7 +12875,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A221" s="5">
         <v>38869</v>
       </c>
@@ -12928,7 +12928,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A222" s="10">
         <v>38838</v>
       </c>
@@ -12981,7 +12981,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A223" s="5">
         <v>38808</v>
       </c>
@@ -13034,7 +13034,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A224" s="10">
         <v>38777</v>
       </c>
@@ -13087,7 +13087,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="225" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A225" s="5">
         <v>38749</v>
       </c>
@@ -13140,7 +13140,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="226" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A226" s="10">
         <v>38718</v>
       </c>
@@ -13193,7 +13193,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="227" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A227" s="5">
         <v>38687</v>
       </c>
@@ -13246,7 +13246,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="228" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A228" s="10">
         <v>38657</v>
       </c>
@@ -13299,7 +13299,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="229" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A229" s="5">
         <v>38626</v>
       </c>
@@ -13352,7 +13352,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="230" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A230" s="10">
         <v>38596</v>
       </c>
@@ -13405,7 +13405,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="231" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A231" s="5">
         <v>38565</v>
       </c>
@@ -13458,7 +13458,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="232" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A232" s="10">
         <v>38534</v>
       </c>
@@ -13511,7 +13511,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="233" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A233" s="5">
         <v>38504</v>
       </c>
@@ -13564,7 +13564,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="234" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A234" s="10">
         <v>38473</v>
       </c>
@@ -13617,7 +13617,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="235" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A235" s="5">
         <v>38443</v>
       </c>
@@ -13670,7 +13670,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="236" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A236" s="10">
         <v>38412</v>
       </c>
@@ -13723,7 +13723,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="237" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A237" s="5">
         <v>38384</v>
       </c>
@@ -13776,7 +13776,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="238" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A238" s="10">
         <v>38353</v>
       </c>
@@ -13829,7 +13829,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="239" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A239" s="5">
         <v>38322</v>
       </c>
@@ -13882,7 +13882,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="240" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A240" s="10">
         <v>38292</v>
       </c>
@@ -13935,7 +13935,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="241" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A241" s="5">
         <v>38261</v>
       </c>
@@ -13988,7 +13988,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="242" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A242" s="10">
         <v>38231</v>
       </c>
@@ -14041,7 +14041,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="243" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A243" s="5">
         <v>38200</v>
       </c>
@@ -14094,7 +14094,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="244" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A244" s="10">
         <v>38169</v>
       </c>
@@ -14147,1272 +14147,1272 @@
         <v>17</v>
       </c>
     </row>
-    <row r="245" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A246" s="5">
         <v>45444</v>
       </c>
     </row>
-    <row r="247" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A247" s="10">
         <v>45413</v>
       </c>
     </row>
-    <row r="248" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A248" s="5">
         <v>45383</v>
       </c>
     </row>
-    <row r="249" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A249" s="10">
         <v>45352</v>
       </c>
     </row>
-    <row r="250" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A250" s="5">
         <v>45323</v>
       </c>
     </row>
-    <row r="251" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A251" s="10">
         <v>45292</v>
       </c>
     </row>
-    <row r="252" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A252" s="5">
         <v>45261</v>
       </c>
     </row>
-    <row r="253" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A253" s="10">
         <v>45231</v>
       </c>
     </row>
-    <row r="254" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A254" s="5">
         <v>45200</v>
       </c>
     </row>
-    <row r="255" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A255" s="10">
         <v>45170</v>
       </c>
     </row>
-    <row r="256" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A256" s="5">
         <v>45139</v>
       </c>
     </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A257" s="10">
         <v>45108</v>
       </c>
     </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A258" s="5">
         <v>45078</v>
       </c>
     </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A259" s="10">
         <v>45047</v>
       </c>
     </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A260" s="5">
         <v>45017</v>
       </c>
     </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A261" s="10">
         <v>44986</v>
       </c>
     </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A262" s="5">
         <v>44958</v>
       </c>
     </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A263" s="10">
         <v>44927</v>
       </c>
     </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A264" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A265" s="5">
         <v>44896</v>
       </c>
     </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A266" s="10">
         <v>44866</v>
       </c>
     </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A267" s="5">
         <v>44835</v>
       </c>
     </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A268" s="10">
         <v>44805</v>
       </c>
     </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A269" s="5">
         <v>44774</v>
       </c>
     </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A270" s="10">
         <v>44743</v>
       </c>
     </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A271" s="5">
         <v>44713</v>
       </c>
     </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A272" s="10">
         <v>44682</v>
       </c>
     </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A273" s="5">
         <v>44652</v>
       </c>
     </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A274" s="10">
         <v>44621</v>
       </c>
     </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A275" s="5">
         <v>44593</v>
       </c>
     </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A276" s="10">
         <v>44562</v>
       </c>
     </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A277" s="5">
         <v>44531</v>
       </c>
     </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A278" s="10">
         <v>44501</v>
       </c>
     </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A279" s="5">
         <v>44470</v>
       </c>
     </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A280" s="10">
         <v>44440</v>
       </c>
     </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A281" s="5">
         <v>44409</v>
       </c>
     </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A282" s="10">
         <v>44378</v>
       </c>
     </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A283" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A284" s="5">
         <v>44348</v>
       </c>
     </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A285" s="10">
         <v>44317</v>
       </c>
     </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A286" s="5">
         <v>44287</v>
       </c>
     </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A287" s="10">
         <v>44256</v>
       </c>
     </row>
-    <row r="288" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A288" s="5">
         <v>44228</v>
       </c>
     </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A289" s="10">
         <v>44197</v>
       </c>
     </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A290" s="5">
         <v>44166</v>
       </c>
     </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A291" s="10">
         <v>44136</v>
       </c>
     </row>
-    <row r="292" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A292" s="5">
         <v>44105</v>
       </c>
     </row>
-    <row r="293" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A293" s="10">
         <v>44075</v>
       </c>
     </row>
-    <row r="294" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A294" s="5">
         <v>44044</v>
       </c>
     </row>
-    <row r="295" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A295" s="10">
         <v>44013</v>
       </c>
     </row>
-    <row r="296" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A296" s="5">
         <v>43983</v>
       </c>
     </row>
-    <row r="297" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A297" s="10">
         <v>43952</v>
       </c>
     </row>
-    <row r="298" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A298" s="5">
         <v>43922</v>
       </c>
     </row>
-    <row r="299" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A299" s="10">
         <v>43891</v>
       </c>
     </row>
-    <row r="300" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A300" s="5">
         <v>43862</v>
       </c>
     </row>
-    <row r="301" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A301" s="10">
         <v>43831</v>
       </c>
     </row>
-    <row r="302" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A302" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A303" s="5">
         <v>43800</v>
       </c>
     </row>
-    <row r="304" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A304" s="10">
         <v>43770</v>
       </c>
     </row>
-    <row r="305" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A305" s="5">
         <v>43739</v>
       </c>
     </row>
-    <row r="306" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A306" s="10">
         <v>43709</v>
       </c>
     </row>
-    <row r="307" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A307" s="5">
         <v>43678</v>
       </c>
     </row>
-    <row r="308" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A308" s="10">
         <v>43647</v>
       </c>
     </row>
-    <row r="309" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A309" s="5">
         <v>43617</v>
       </c>
     </row>
-    <row r="310" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A310" s="10">
         <v>43586</v>
       </c>
     </row>
-    <row r="311" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A311" s="5">
         <v>43556</v>
       </c>
     </row>
-    <row r="312" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A312" s="10">
         <v>43525</v>
       </c>
     </row>
-    <row r="313" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A313" s="5">
         <v>43497</v>
       </c>
     </row>
-    <row r="314" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A314" s="10">
         <v>43466</v>
       </c>
     </row>
-    <row r="315" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A315" s="5">
         <v>43435</v>
       </c>
     </row>
-    <row r="316" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A316" s="10">
         <v>43405</v>
       </c>
     </row>
-    <row r="317" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A317" s="5">
         <v>43374</v>
       </c>
     </row>
-    <row r="318" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A318" s="10">
         <v>43344</v>
       </c>
     </row>
-    <row r="319" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A319" s="5">
         <v>43313</v>
       </c>
     </row>
-    <row r="320" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A320" s="10">
         <v>43282</v>
       </c>
     </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A321" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A322" s="5">
         <v>43252</v>
       </c>
     </row>
-    <row r="323" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A323" s="10">
         <v>43221</v>
       </c>
     </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A324" s="5">
         <v>43191</v>
       </c>
     </row>
-    <row r="325" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A325" s="10">
         <v>43160</v>
       </c>
     </row>
-    <row r="326" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A326" s="5">
         <v>43132</v>
       </c>
     </row>
-    <row r="327" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A327" s="10">
         <v>43101</v>
       </c>
     </row>
-    <row r="328" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A328" s="5">
         <v>43070</v>
       </c>
     </row>
-    <row r="329" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A329" s="10">
         <v>43040</v>
       </c>
     </row>
-    <row r="330" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A330" s="5">
         <v>43009</v>
       </c>
     </row>
-    <row r="331" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A331" s="10">
         <v>42979</v>
       </c>
     </row>
-    <row r="332" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A332" s="5">
         <v>42948</v>
       </c>
     </row>
-    <row r="333" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A333" s="10">
         <v>42917</v>
       </c>
     </row>
-    <row r="334" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A334" s="5">
         <v>42887</v>
       </c>
     </row>
-    <row r="335" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A335" s="10">
         <v>42856</v>
       </c>
     </row>
-    <row r="336" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A336" s="5">
         <v>42826</v>
       </c>
     </row>
-    <row r="337" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A337" s="10">
         <v>42795</v>
       </c>
     </row>
-    <row r="338" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="338" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A338" s="5">
         <v>42767</v>
       </c>
     </row>
-    <row r="339" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A339" s="10">
         <v>42736</v>
       </c>
     </row>
-    <row r="340" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A340" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A341" s="5">
         <v>42705</v>
       </c>
     </row>
-    <row r="342" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A342" s="10">
         <v>42675</v>
       </c>
     </row>
-    <row r="343" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A343" s="5">
         <v>42644</v>
       </c>
     </row>
-    <row r="344" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A344" s="10">
         <v>42614</v>
       </c>
     </row>
-    <row r="345" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A345" s="5">
         <v>42583</v>
       </c>
     </row>
-    <row r="346" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A346" s="10">
         <v>42552</v>
       </c>
     </row>
-    <row r="347" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A347" s="5">
         <v>42522</v>
       </c>
     </row>
-    <row r="348" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A348" s="10">
         <v>42491</v>
       </c>
     </row>
-    <row r="349" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A349" s="5">
         <v>42461</v>
       </c>
     </row>
-    <row r="350" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A350" s="10">
         <v>42430</v>
       </c>
     </row>
-    <row r="351" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A351" s="5">
         <v>42401</v>
       </c>
     </row>
-    <row r="352" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A352" s="10">
         <v>42370</v>
       </c>
     </row>
-    <row r="353" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="353" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A353" s="5">
         <v>42339</v>
       </c>
     </row>
-    <row r="354" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="354" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A354" s="10">
         <v>42309</v>
       </c>
     </row>
-    <row r="355" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="355" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A355" s="5">
         <v>42278</v>
       </c>
     </row>
-    <row r="356" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A356" s="10">
         <v>42248</v>
       </c>
     </row>
-    <row r="357" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="357" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A357" s="5">
         <v>42217</v>
       </c>
     </row>
-    <row r="358" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="358" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A358" s="10">
         <v>42186</v>
       </c>
     </row>
-    <row r="359" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="359" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A359" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="360" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A360" s="5">
         <v>42156</v>
       </c>
     </row>
-    <row r="361" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="361" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A361" s="10">
         <v>42125</v>
       </c>
     </row>
-    <row r="362" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="362" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A362" s="5">
         <v>42095</v>
       </c>
     </row>
-    <row r="363" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="363" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A363" s="10">
         <v>42064</v>
       </c>
     </row>
-    <row r="364" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A364" s="5">
         <v>42036</v>
       </c>
     </row>
-    <row r="365" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="365" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A365" s="10">
         <v>42005</v>
       </c>
     </row>
-    <row r="366" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="366" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A366" s="5">
         <v>41974</v>
       </c>
     </row>
-    <row r="367" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="367" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A367" s="10">
         <v>41944</v>
       </c>
     </row>
-    <row r="368" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="368" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A368" s="5">
         <v>41913</v>
       </c>
     </row>
-    <row r="369" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="369" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A369" s="10">
         <v>41883</v>
       </c>
     </row>
-    <row r="370" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="370" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A370" s="5">
         <v>41852</v>
       </c>
     </row>
-    <row r="371" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="371" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A371" s="10">
         <v>41821</v>
       </c>
     </row>
-    <row r="372" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="372" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A372" s="5">
         <v>41791</v>
       </c>
     </row>
-    <row r="373" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="373" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A373" s="10">
         <v>41760</v>
       </c>
     </row>
-    <row r="374" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="374" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A374" s="5">
         <v>41730</v>
       </c>
     </row>
-    <row r="375" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="375" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A375" s="10">
         <v>41699</v>
       </c>
     </row>
-    <row r="376" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="376" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A376" s="5">
         <v>41671</v>
       </c>
     </row>
-    <row r="377" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="377" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A377" s="10">
         <v>41640</v>
       </c>
     </row>
-    <row r="378" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="378" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A378" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="379" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A379" s="5">
         <v>41609</v>
       </c>
     </row>
-    <row r="380" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="380" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A380" s="10">
         <v>41579</v>
       </c>
     </row>
-    <row r="381" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="381" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A381" s="5">
         <v>41548</v>
       </c>
     </row>
-    <row r="382" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="382" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A382" s="10">
         <v>41518</v>
       </c>
     </row>
-    <row r="383" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="383" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A383" s="5">
         <v>41487</v>
       </c>
     </row>
-    <row r="384" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="384" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A384" s="10">
         <v>41456</v>
       </c>
     </row>
-    <row r="385" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="385" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A385" s="5">
         <v>41426</v>
       </c>
     </row>
-    <row r="386" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="386" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A386" s="10">
         <v>41395</v>
       </c>
     </row>
-    <row r="387" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="387" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A387" s="5">
         <v>41365</v>
       </c>
     </row>
-    <row r="388" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="388" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A388" s="10">
         <v>41334</v>
       </c>
     </row>
-    <row r="389" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="389" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A389" s="5">
         <v>41306</v>
       </c>
     </row>
-    <row r="390" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="390" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A390" s="10">
         <v>41275</v>
       </c>
     </row>
-    <row r="391" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="391" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A391" s="5">
         <v>41244</v>
       </c>
     </row>
-    <row r="392" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="392" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A392" s="10">
         <v>41214</v>
       </c>
     </row>
-    <row r="393" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="393" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A393" s="5">
         <v>41183</v>
       </c>
     </row>
-    <row r="394" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="394" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A394" s="10">
         <v>41153</v>
       </c>
     </row>
-    <row r="395" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="395" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A395" s="5">
         <v>41122</v>
       </c>
     </row>
-    <row r="396" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="396" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A396" s="10">
         <v>41091</v>
       </c>
     </row>
-    <row r="397" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="397" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A397" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="398" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A398" s="5">
         <v>41061</v>
       </c>
     </row>
-    <row r="399" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="399" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A399" s="10">
         <v>41030</v>
       </c>
     </row>
-    <row r="400" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="400" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A400" s="5">
         <v>41000</v>
       </c>
     </row>
-    <row r="401" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="401" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A401" s="10">
         <v>40969</v>
       </c>
     </row>
-    <row r="402" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="402" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A402" s="5">
         <v>40940</v>
       </c>
     </row>
-    <row r="403" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="403" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A403" s="10">
         <v>40909</v>
       </c>
     </row>
-    <row r="404" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="404" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A404" s="5">
         <v>40878</v>
       </c>
     </row>
-    <row r="405" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="405" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A405" s="10">
         <v>40848</v>
       </c>
     </row>
-    <row r="406" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="406" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A406" s="5">
         <v>40817</v>
       </c>
     </row>
-    <row r="407" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="407" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A407" s="10">
         <v>40787</v>
       </c>
     </row>
-    <row r="408" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="408" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A408" s="5">
         <v>40756</v>
       </c>
     </row>
-    <row r="409" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="409" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A409" s="10">
         <v>40725</v>
       </c>
     </row>
-    <row r="410" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="410" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A410" s="5">
         <v>40695</v>
       </c>
     </row>
-    <row r="411" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="411" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A411" s="10">
         <v>40664</v>
       </c>
     </row>
-    <row r="412" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="412" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A412" s="5">
         <v>40634</v>
       </c>
     </row>
-    <row r="413" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="413" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A413" s="10">
         <v>40603</v>
       </c>
     </row>
-    <row r="414" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="414" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A414" s="5">
         <v>40575</v>
       </c>
     </row>
-    <row r="415" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="415" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A415" s="10">
         <v>40544</v>
       </c>
     </row>
-    <row r="416" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="416" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A416" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="417" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A417" s="5">
         <v>40513</v>
       </c>
     </row>
-    <row r="418" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="418" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A418" s="10">
         <v>40483</v>
       </c>
     </row>
-    <row r="419" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="419" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A419" s="5">
         <v>40452</v>
       </c>
     </row>
-    <row r="420" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="420" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A420" s="10">
         <v>40422</v>
       </c>
     </row>
-    <row r="421" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="421" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A421" s="5">
         <v>40391</v>
       </c>
     </row>
-    <row r="422" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="422" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A422" s="10">
         <v>40360</v>
       </c>
     </row>
-    <row r="423" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="423" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A423" s="5">
         <v>40330</v>
       </c>
     </row>
-    <row r="424" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="424" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A424" s="10">
         <v>40299</v>
       </c>
     </row>
-    <row r="425" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="425" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A425" s="5">
         <v>40269</v>
       </c>
     </row>
-    <row r="426" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="426" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A426" s="10">
         <v>40238</v>
       </c>
     </row>
-    <row r="427" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="427" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A427" s="5">
         <v>40210</v>
       </c>
     </row>
-    <row r="428" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="428" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A428" s="10">
         <v>40179</v>
       </c>
     </row>
-    <row r="429" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="429" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A429" s="5">
         <v>40148</v>
       </c>
     </row>
-    <row r="430" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="430" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A430" s="10">
         <v>40118</v>
       </c>
     </row>
-    <row r="431" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="431" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A431" s="5">
         <v>40087</v>
       </c>
     </row>
-    <row r="432" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="432" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A432" s="10">
         <v>40057</v>
       </c>
     </row>
-    <row r="433" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="433" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A433" s="5">
         <v>40026</v>
       </c>
     </row>
-    <row r="434" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="434" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A434" s="10">
         <v>39995</v>
       </c>
     </row>
-    <row r="435" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A435" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="436" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A436" s="5">
         <v>39965</v>
       </c>
     </row>
-    <row r="437" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="437" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A437" s="10">
         <v>39934</v>
       </c>
     </row>
-    <row r="438" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="438" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A438" s="5">
         <v>39904</v>
       </c>
     </row>
-    <row r="439" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="439" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A439" s="10">
         <v>39873</v>
       </c>
     </row>
-    <row r="440" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="440" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A440" s="5">
         <v>39845</v>
       </c>
     </row>
-    <row r="441" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A441" s="10">
         <v>39814</v>
       </c>
     </row>
-    <row r="442" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="442" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A442" s="5">
         <v>39783</v>
       </c>
     </row>
-    <row r="443" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="443" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A443" s="10">
         <v>39753</v>
       </c>
     </row>
-    <row r="444" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="444" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A444" s="5">
         <v>39722</v>
       </c>
     </row>
-    <row r="445" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="445" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A445" s="10">
         <v>39692</v>
       </c>
     </row>
-    <row r="446" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="446" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A446" s="5">
         <v>39661</v>
       </c>
     </row>
-    <row r="447" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="447" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A447" s="10">
         <v>39630</v>
       </c>
     </row>
-    <row r="448" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="448" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A448" s="5">
         <v>39600</v>
       </c>
     </row>
-    <row r="449" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="449" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A449" s="10">
         <v>39569</v>
       </c>
     </row>
-    <row r="450" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="450" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A450" s="5">
         <v>39539</v>
       </c>
     </row>
-    <row r="451" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="451" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A451" s="10">
         <v>39508</v>
       </c>
     </row>
-    <row r="452" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="452" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A452" s="5">
         <v>39479</v>
       </c>
     </row>
-    <row r="453" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="453" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A453" s="10">
         <v>39448</v>
       </c>
     </row>
-    <row r="454" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="454" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A454" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="455" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A455" s="5">
         <v>39417</v>
       </c>
     </row>
-    <row r="456" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="456" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A456" s="10">
         <v>39387</v>
       </c>
     </row>
-    <row r="457" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="457" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A457" s="5">
         <v>39356</v>
       </c>
     </row>
-    <row r="458" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="458" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A458" s="10">
         <v>39326</v>
       </c>
     </row>
-    <row r="459" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="459" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A459" s="5">
         <v>39295</v>
       </c>
     </row>
-    <row r="460" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="460" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A460" s="10">
         <v>39264</v>
       </c>
     </row>
-    <row r="461" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="461" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A461" s="5">
         <v>39234</v>
       </c>
     </row>
-    <row r="462" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="462" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A462" s="10">
         <v>39203</v>
       </c>
     </row>
-    <row r="463" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="463" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A463" s="5">
         <v>39173</v>
       </c>
     </row>
-    <row r="464" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="464" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A464" s="10">
         <v>39142</v>
       </c>
     </row>
-    <row r="465" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="465" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A465" s="5">
         <v>39114</v>
       </c>
     </row>
-    <row r="466" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="466" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A466" s="10">
         <v>39083</v>
       </c>
     </row>
-    <row r="467" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="467" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A467" s="5">
         <v>39052</v>
       </c>
     </row>
-    <row r="468" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="468" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A468" s="10">
         <v>39022</v>
       </c>
     </row>
-    <row r="469" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="469" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A469" s="5">
         <v>38991</v>
       </c>
     </row>
-    <row r="470" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="470" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A470" s="10">
         <v>38961</v>
       </c>
     </row>
-    <row r="471" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="471" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A471" s="5">
         <v>38930</v>
       </c>
     </row>
-    <row r="472" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="472" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A472" s="10">
         <v>38899</v>
       </c>
     </row>
-    <row r="473" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="473" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A473" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="474" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="474" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A474" s="5">
         <v>38869</v>
       </c>
     </row>
-    <row r="475" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="475" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A475" s="10">
         <v>38838</v>
       </c>
     </row>
-    <row r="476" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="476" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A476" s="5">
         <v>38808</v>
       </c>
     </row>
-    <row r="477" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="477" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A477" s="10">
         <v>38777</v>
       </c>
     </row>
-    <row r="478" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="478" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A478" s="5">
         <v>38749</v>
       </c>
     </row>
-    <row r="479" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="479" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A479" s="10">
         <v>38718</v>
       </c>
     </row>
-    <row r="480" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="480" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A480" s="5">
         <v>38687</v>
       </c>
     </row>
-    <row r="481" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="481" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A481" s="10">
         <v>38657</v>
       </c>
     </row>
-    <row r="482" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="482" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A482" s="5">
         <v>38626</v>
       </c>
     </row>
-    <row r="483" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="483" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A483" s="10">
         <v>38596</v>
       </c>
     </row>
-    <row r="484" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="484" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A484" s="5">
         <v>38565</v>
       </c>
     </row>
-    <row r="485" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="485" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A485" s="10">
         <v>38534</v>
       </c>
     </row>
-    <row r="486" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="486" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A486" s="5">
         <v>38504</v>
       </c>
     </row>
-    <row r="487" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="487" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A487" s="10">
         <v>38473</v>
       </c>
     </row>
-    <row r="488" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="488" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A488" s="5">
         <v>38443</v>
       </c>
     </row>
-    <row r="489" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="489" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A489" s="10">
         <v>38412</v>
       </c>
     </row>
-    <row r="490" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="490" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A490" s="5">
         <v>38384</v>
       </c>
     </row>
-    <row r="491" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="491" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A491" s="10">
         <v>38353</v>
       </c>
     </row>
-    <row r="492" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="492" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A492" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="493" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="493" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A493" s="5">
         <v>38322</v>
       </c>
     </row>
-    <row r="494" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="494" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A494" s="10">
         <v>38292</v>
       </c>
     </row>
-    <row r="495" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="495" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A495" s="5">
         <v>38261</v>
       </c>
     </row>
-    <row r="496" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="496" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A496" s="10">
         <v>38231</v>
       </c>
     </row>
-    <row r="497" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="497" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A497" s="5">
         <v>38200</v>
       </c>
     </row>
-    <row r="498" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="498" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A498" s="10">
         <v>38169</v>
       </c>
